--- a/mock-data/budget-master-data.xlsx
+++ b/mock-data/budget-master-data.xlsx
@@ -1244,7 +1244,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">

--- a/mock-data/budget-master-data.xlsx
+++ b/mock-data/budget-master-data.xlsx
@@ -539,7 +539,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>GP-ACME</t>
+          <t>GP-CONT</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>RD-ACME-NA</t>
+          <t>RD-CONT-NA</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>BR-ACME-MW</t>
+          <t>BR-GLP-MW</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>BR-ACME-NE</t>
+          <t>BR-GLP-NE</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>BR-GLOBEX-WEST</t>
+          <t>BR-PCBK-WEST</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>BR-ACME-MW</t>
+          <t>BR-GLP-MW</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>BR-ACME-MW</t>
+          <t>BR-GLP-MW</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>BR-ACME-NE</t>
+          <t>BR-GLP-NE</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>BR-GLOBEX-WEST</t>
+          <t>BR-PCBK-WEST</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>BR-ACME-MW</t>
+          <t>BR-GLP-MW</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>RD-ACME-NA</t>
+          <t>RD-CONT-NA</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>GP-ACME</t>
+          <t>GP-CONT</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>BR-GLOBEX-WEST</t>
+          <t>BR-PCBK-WEST</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>BR-ACME-MW</t>
+          <t>BR-GLP-MW</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>BR-ACME-MW</t>
+          <t>BR-GLP-MW</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>BR-ACME-NE</t>
+          <t>BR-GLP-NE</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>BR-GLOBEX-WEST</t>
+          <t>BR-PCBK-WEST</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">

--- a/mock-data/budget-master-data.xlsx
+++ b/mock-data/budget-master-data.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cost_Centers" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Approval_Matrix" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buyer_Authority" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Approvers" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1264,4 +1265,188 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>APPROVERS  (named approvers, role, contact, approval limit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>approver_id</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>approver_name</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>approval_limit_amount</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>APR-501</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Karen Wells</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>BRANCH_MANAGER</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>karen.wells@glps.com</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>APR-502</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>David Cho</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>REGIONAL_MANAGER</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>david.cho@glps.com</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>250000</v>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>APR-503</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Ana Reyes</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>BRANCH_MANAGER</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>ana.reyes@pcbk.com</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>60000</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>APR-504</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Procurement Board</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>CORPORATE_PROCUREMENT</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>procurement.board@continental-bpg.com</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>99999999</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/mock-data/budget-master-data.xlsx
+++ b/mock-data/budget-master-data.xlsx
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>80000</v>
+        <v>300000</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>78000</v>
+        <v>100000</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>2000</v>
+        <v>200000</v>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
@@ -1191,11 +1191,11 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>5000</v>
+        <v>200000</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
